--- a/Cost model - Metal support.xlsx
+++ b/Cost model - Metal support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fskna_dtu_dk/Documents/Papers DTU Energy/Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{E0D21C74-1E67-4195-BB1C-BE0343C9FF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{773FEB7D-F195-41CE-A0E4-AC61B0BD1A4A}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{E0D21C74-1E67-4195-BB1C-BE0343C9FF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58DE86E3-D2CC-4D41-8490-79CF74D95CA8}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
+    <workbookView xWindow="3150" yWindow="3660" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Manufacturing results" sheetId="8" r:id="rId1"/>
@@ -1472,7 +1472,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1571,11 +1571,6 @@
     <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="181" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2131,7 +2126,7 @@
                 <c:formatCode>_-* #,##0.0000_-;\-* #,##0.0000_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.180314494680851E-3</c:v>
+                  <c:v>4.677947473404255E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2.9716958522995798E-3</c:v>
@@ -2519,7 +2514,7 @@
                   <c:v>9.8578723404255325E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.488164893617021E-4</c:v>
+                  <c:v>7.4644946808510631E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3.1931449468085104E-4</c:v>
@@ -9015,14 +9010,14 @@
       </c>
       <c r="B2" s="57">
         <f>SUM(B4:B9)</f>
-        <v>7.7258752642879985E-2</v>
+        <v>7.7756385621603391E-2</v>
       </c>
       <c r="C2" t="s">
         <v>275</v>
       </c>
       <c r="D2" s="7">
         <f>SUM(D4:D9)</f>
-        <v>6.1807002114303993</v>
+        <v>6.2205108497282717</v>
       </c>
       <c r="E2" t="s">
         <v>276</v>
@@ -9036,7 +9031,7 @@
       </c>
       <c r="P2" s="7">
         <f>SUM(P4:P9)</f>
-        <v>370.84201268582393</v>
+        <v>373.23065098369631</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -9045,14 +9040,14 @@
       </c>
       <c r="B4" s="35">
         <f>SUM(Cell!L3:L1048576)/'Cross-layer'!B24</f>
-        <v>4.180314494680851E-3</v>
+        <v>4.677947473404255E-3</v>
       </c>
       <c r="C4" t="s">
         <v>275</v>
       </c>
       <c r="D4" s="11">
         <f>SUM(Cell!L3:L1048576)</f>
-        <v>0.33442515957446806</v>
+        <v>0.3742357978723404</v>
       </c>
       <c r="E4" t="s">
         <v>276</v>
@@ -9066,7 +9061,7 @@
       </c>
       <c r="P4" s="7">
         <f>D4*'Cross-layer'!$B$3</f>
-        <v>20.065509574468084</v>
+        <v>22.454147872340425</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -9218,11 +9213,11 @@
       </c>
       <c r="B13" s="23">
         <f>SUM(B14:B19)</f>
-        <v>4.180314494680851E-3</v>
+        <v>4.677947473404255E-3</v>
       </c>
       <c r="C13" s="24">
         <f>SUM(C14:C19)</f>
-        <v>0.33442515957446806</v>
+        <v>0.3742357978723404</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -9271,11 +9266,11 @@
       </c>
       <c r="B17" s="28">
         <f>Cell!L6/'Cross-layer'!$B$24</f>
-        <v>2.488164893617021E-4</v>
+        <v>7.4644946808510631E-4</v>
       </c>
       <c r="C17" s="29">
         <f>B17*'Cross-layer'!$B$24</f>
-        <v>1.9905319148936167E-2</v>
+        <v>5.9715957446808507E-2</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -9675,7 +9670,7 @@
       </c>
       <c r="B50" s="7">
         <f>D2/$B$48</f>
-        <v>120.6111326642603</v>
+        <v>121.38800357094392</v>
       </c>
       <c r="C50" t="s">
         <v>303</v>
@@ -9687,7 +9682,7 @@
       </c>
       <c r="B52" s="7">
         <f>D4/$B$48</f>
-        <v>6.5260238982482157</v>
+        <v>7.3028948049318343</v>
       </c>
       <c r="C52" t="s">
         <v>303</v>
@@ -11480,13 +11475,12 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="97"/>
+      <c r="B12" s="17"/>
       <c r="I12" s="72" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="99"/>
       <c r="E13" t="s">
         <v>365</v>
       </c>
@@ -11509,7 +11503,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="97"/>
+      <c r="B14" s="17"/>
       <c r="E14" t="s">
         <v>369</v>
       </c>
@@ -11532,7 +11526,6 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="99"/>
       <c r="E15" t="s">
         <v>373</v>
       </c>
@@ -11548,14 +11541,14 @@
       </c>
       <c r="J15" s="81">
         <f>'Manufacturing results'!D2*F11</f>
-        <v>370.84201268582393</v>
+        <v>373.23065098369631</v>
       </c>
       <c r="K15" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="100"/>
+      <c r="B16" s="36"/>
       <c r="E16" t="s">
         <v>374</v>
       </c>
@@ -11571,14 +11564,13 @@
       </c>
       <c r="J16" s="18">
         <f>J15/J8</f>
-        <v>120.6111326642603</v>
+        <v>121.38800357094392</v>
       </c>
       <c r="K16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="99"/>
+    <row r="17" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>376</v>
       </c>
@@ -11600,7 +11592,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>371</v>
       </c>
@@ -11612,7 +11604,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>377</v>
       </c>
@@ -11624,45 +11616,45 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J20" s="14"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I22" s="72"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E23" s="72"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F24" s="96"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F25" s="96"/>
+    <row r="24" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="14"/>
+    </row>
+    <row r="25" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F25" s="14"/>
       <c r="J25" s="70"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F26" s="96"/>
+    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F26" s="14"/>
       <c r="J26" s="17"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E27" s="14"/>
-      <c r="F27" s="97"/>
+      <c r="F27" s="17"/>
       <c r="J27" s="17"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F28" s="96"/>
+    <row r="28" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F28" s="14"/>
       <c r="G28" s="36"/>
       <c r="J28" s="17"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F29" s="98"/>
+    <row r="29" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="8"/>
       <c r="G29" s="36"/>
       <c r="J29" s="17"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J30" s="14"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:11" x14ac:dyDescent="0.25">
       <c r="I32" s="72"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -12768,11 +12760,11 @@
         <v>116</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="C6">
         <f>_xlfn.XLOOKUP(B6,Tabel2[Material],Tabel2[Cost],"Not found")</f>
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D6" s="21">
         <v>10</v>
@@ -12797,7 +12789,7 @@
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>1.8900000000000001</v>
+        <v>5.67</v>
       </c>
       <c r="K6">
         <f>'Cross-layer'!$B$25</f>
@@ -12805,7 +12797,7 @@
       </c>
       <c r="L6" s="4">
         <f>K6/100/100*J6/(1-'Cross-layer'!$B$19)</f>
-        <v>1.990531914893617E-2</v>
+        <v>5.9715957446808507E-2</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="3"/>

--- a/Cost model - Metal support.xlsx
+++ b/Cost model - Metal support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fskna_dtu_dk/Documents/Papers DTU Energy/Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{E0D21C74-1E67-4195-BB1C-BE0343C9FF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58DE86E3-D2CC-4D41-8490-79CF74D95CA8}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{E0D21C74-1E67-4195-BB1C-BE0343C9FF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8492638-2317-421A-B52E-2A4342C5E532}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3660" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
+    <workbookView xWindow="3150" yWindow="3660" windowWidth="28800" windowHeight="15345" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Manufacturing results" sheetId="8" r:id="rId1"/>
@@ -1884,6 +1884,15 @@
       <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _k_r_._-;\-* #,##0.00\ _k_r_._-;_-* &quot;-&quot;??\ _k_r_._-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -1977,15 +1986,6 @@
           <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _k_r_._-;\-* #,##0.00\ _k_r_._-;_-* &quot;-&quot;??\ _k_r_._-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2126,7 +2126,7 @@
                 <c:formatCode>_-* #,##0.0000_-;\-* #,##0.0000_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.677947473404255E-3</c:v>
+                  <c:v>4.6068570478723396E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2.9716958522995798E-3</c:v>
@@ -2514,7 +2514,7 @@
                   <c:v>9.8578723404255325E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.4644946808510631E-4</c:v>
+                  <c:v>6.7535904255319138E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3.1931449468085104E-4</c:v>
@@ -8503,10 +8503,10 @@
     <tableColumn id="1" xr3:uid="{6FB9D1BB-862C-4265-9888-B904928F548B}" name="Table for max cycle time"/>
     <tableColumn id="2" xr3:uid="{B29FA2DB-E433-4BBD-9C5B-B20EDA4F5EFE}" name="Shifts/day"/>
     <tableColumn id="3" xr3:uid="{7152D10B-3160-4CAA-B82C-16A2C5D39A84}" name="Hours/shift"/>
-    <tableColumn id="5" xr3:uid="{9C38729E-989F-48A5-81DB-73C26C42715E}" name="Hours/year" dataDxfId="30">
+    <tableColumn id="5" xr3:uid="{9C38729E-989F-48A5-81DB-73C26C42715E}" name="Hours/year" dataDxfId="21">
       <calculatedColumnFormula>$B$12*Max_cycle_table[[#This Row],[Shifts/day]]*Max_cycle_table[[#This Row],[Hours/shift]]*$B$11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{48339CBF-7A02-4836-95BE-5B7504B08E0E}" name="Takt time" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{48339CBF-7A02-4836-95BE-5B7504B08E0E}" name="Takt time" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8517,7 +8517,7 @@
   <autoFilter ref="A18:B22" xr:uid="{F62534EA-BF6F-4318-8B4F-D28B5089AFA8}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{EA796442-16E2-4E20-ABD3-CCB04AE01814}" name="Scaling factors"/>
-    <tableColumn id="2" xr3:uid="{BF569A97-F08D-484A-891B-D0C8F9EBE3FC}" name="Value" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{BF569A97-F08D-484A-891B-D0C8F9EBE3FC}" name="Value" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8528,32 +8528,32 @@
   <autoFilter ref="A2:M10" xr:uid="{0D34BDA9-C6D6-4A08-9C67-A55F5671020A}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{91AAE088-8C76-413F-9D94-77943C07C31F}" name="Layer"/>
-    <tableColumn id="2" xr3:uid="{0DFAD7F0-3B79-47F1-AB7F-1BA5B8732471}" name="Material" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{0DFAD7F0-3B79-47F1-AB7F-1BA5B8732471}" name="Material" dataDxfId="30"/>
     <tableColumn id="3" xr3:uid="{84B8C74A-F42F-4AA2-9C3A-D78BA44DB750}" name="Mat. Price">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B3,Tabel2[Material],Tabel2[Cost],"Not found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4BCAD362-8724-4FF6-9239-38C233A23890}" name="Thickness" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{55ECBF23-7787-4952-A6D5-34A861F6F6C4}" name="Porosity" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{196D43A2-0F28-4197-981C-171BC1FA8653}" name="Fraction in layer" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{E047549B-9CAC-47A4-8094-0417F7FCD059}" name="Volume%" dataDxfId="23">
+    <tableColumn id="4" xr3:uid="{4BCAD362-8724-4FF6-9239-38C233A23890}" name="Thickness" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{55ECBF23-7787-4952-A6D5-34A861F6F6C4}" name="Porosity" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{196D43A2-0F28-4197-981C-171BC1FA8653}" name="Fraction in layer" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{E047549B-9CAC-47A4-8094-0417F7FCD059}" name="Volume%" dataDxfId="26">
       <calculatedColumnFormula>F3*(1-E3)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{F0EDB6E0-987C-41D3-B4FF-9CE9A0BBFC85}" name="Mat. Density">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B3,Tabel2[Material],Tabel2[Density],"Not found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{02AB3D05-0FAA-4491-8FDB-F7DBD8DB728A}" name="Mass" dataDxfId="22">
+    <tableColumn id="9" xr3:uid="{02AB3D05-0FAA-4491-8FDB-F7DBD8DB728A}" name="Mass" dataDxfId="25">
       <calculatedColumnFormula>H3*G3*D3/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3D46FF12-3B7C-48FB-B620-A47DCD010057}" name="Cost per area" dataDxfId="21">
+    <tableColumn id="10" xr3:uid="{3D46FF12-3B7C-48FB-B620-A47DCD010057}" name="Cost per area" dataDxfId="24">
       <calculatedColumnFormula>I3*C3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{CF75B717-FC37-4210-BC6C-49B7DEA7F77A}" name="Area">
       <calculatedColumnFormula>'Cross-layer'!$B$25</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{C1406905-0770-4F36-B968-520FC22BD12F}" name="Cost per unit" dataDxfId="20">
+    <tableColumn id="12" xr3:uid="{C1406905-0770-4F36-B968-520FC22BD12F}" name="Cost per unit" dataDxfId="23">
       <calculatedColumnFormula>K3/100/100*J3/(1-'Cross-layer'!$B$19)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{23C22564-C175-49D3-9637-1D7E243A1AF5}" name="Mass per unit" dataDxfId="19">
+    <tableColumn id="13" xr3:uid="{23C22564-C175-49D3-9637-1D7E243A1AF5}" name="Mass per unit" dataDxfId="22">
       <calculatedColumnFormula>K3/100/100*I3*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9010,28 +9010,28 @@
       </c>
       <c r="B2" s="57">
         <f>SUM(B4:B9)</f>
-        <v>7.7756385621603391E-2</v>
+        <v>7.768529519607148E-2</v>
       </c>
       <c r="C2" t="s">
         <v>275</v>
       </c>
       <c r="D2" s="7">
         <f>SUM(D4:D9)</f>
-        <v>6.2205108497282717</v>
+        <v>6.2148236156857184</v>
       </c>
       <c r="E2" t="s">
         <v>276</v>
       </c>
       <c r="F2" s="7">
         <f>SUM(F4:F6)</f>
-        <v>194.20169577588698</v>
+        <v>194.14229577588699</v>
       </c>
       <c r="G2" t="s">
         <v>269</v>
       </c>
       <c r="P2" s="7">
         <f>SUM(P4:P9)</f>
-        <v>373.23065098369631</v>
+        <v>372.88941694114311</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -9040,28 +9040,28 @@
       </c>
       <c r="B4" s="35">
         <f>SUM(Cell!L3:L1048576)/'Cross-layer'!B24</f>
-        <v>4.677947473404255E-3</v>
+        <v>4.6068570478723396E-3</v>
       </c>
       <c r="C4" t="s">
         <v>275</v>
       </c>
       <c r="D4" s="11">
         <f>SUM(Cell!L3:L1048576)</f>
-        <v>0.3742357978723404</v>
+        <v>0.36854856382978718</v>
       </c>
       <c r="E4" t="s">
         <v>276</v>
       </c>
       <c r="F4" s="7">
         <f>SUM(Cell!M3:M1048576)</f>
-        <v>19.678409999999996</v>
+        <v>19.619009999999996</v>
       </c>
       <c r="G4" t="s">
         <v>269</v>
       </c>
       <c r="P4" s="7">
         <f>D4*'Cross-layer'!$B$3</f>
-        <v>22.454147872340425</v>
+        <v>22.112913829787232</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -9213,11 +9213,11 @@
       </c>
       <c r="B13" s="23">
         <f>SUM(B14:B19)</f>
-        <v>4.677947473404255E-3</v>
+        <v>4.6068570478723404E-3</v>
       </c>
       <c r="C13" s="24">
         <f>SUM(C14:C19)</f>
-        <v>0.3742357978723404</v>
+        <v>0.36854856382978718</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -9266,11 +9266,11 @@
       </c>
       <c r="B17" s="28">
         <f>Cell!L6/'Cross-layer'!$B$24</f>
-        <v>7.4644946808510631E-4</v>
+        <v>6.7535904255319138E-4</v>
       </c>
       <c r="C17" s="29">
         <f>B17*'Cross-layer'!$B$24</f>
-        <v>5.9715957446808507E-2</v>
+        <v>5.4028723404255311E-2</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="B50" s="7">
         <f>D2/$B$48</f>
-        <v>121.38800357094392</v>
+        <v>121.27702201284626</v>
       </c>
       <c r="C50" t="s">
         <v>303</v>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="B52" s="7">
         <f>D4/$B$48</f>
-        <v>7.3028948049318343</v>
+        <v>7.191913246834174</v>
       </c>
       <c r="C52" t="s">
         <v>303</v>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="J15" s="81">
         <f>'Manufacturing results'!D2*F11</f>
-        <v>373.23065098369631</v>
+        <v>372.88941694114311</v>
       </c>
       <c r="K15" t="s">
         <v>362</v>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="J16" s="18">
         <f>J15/J8</f>
-        <v>121.38800357094392</v>
+        <v>121.27702201284626</v>
       </c>
       <c r="K16" t="s">
         <v>364</v>
@@ -12781,15 +12781,15 @@
       </c>
       <c r="H6">
         <f>_xlfn.XLOOKUP(B6,Tabel2[Material],Tabel2[Density],"Not found")</f>
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="1"/>
-        <v>6.3E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="2"/>
-        <v>5.67</v>
+        <v>5.13</v>
       </c>
       <c r="K6">
         <f>'Cross-layer'!$B$25</f>
@@ -12797,11 +12797,11 @@
       </c>
       <c r="L6" s="4">
         <f>K6/100/100*J6/(1-'Cross-layer'!$B$19)</f>
-        <v>5.9715957446808507E-2</v>
+        <v>5.4028723404255311E-2</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="3"/>
-        <v>0.62369999999999992</v>
+        <v>0.56430000000000002</v>
       </c>
       <c r="O6" t="s">
         <v>118</v>
@@ -16557,7 +16557,7 @@
         <v>90</v>
       </c>
       <c r="C5">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
